--- a/tests/fixtures/projects.xlsx
+++ b/tests/fixtures/projects.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>estimated_completion_date</t>
+          <t>target_date</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
